--- a/DataTables/Datas/#VSWave.xlsx
+++ b/DataTables/Datas/#VSWave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>speedMul</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>isElite</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>viewScale</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +576,16 @@
           <t>移速系数(敌人表基础移速x此值)</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>是否精英(true=到点一次性刷一批,死亡掉宝箱)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>放大系数(视觉与碰撞半径同步放大)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
@@ -580,6 +610,14 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -608,6 +646,14 @@
       <c r="I5" t="n">
         <v>1</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -634,6 +680,14 @@
       <c r="I6" t="n">
         <v>1.1</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -660,6 +714,14 @@
       <c r="I7" t="n">
         <v>1.8</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -686,6 +748,14 @@
       <c r="I8" t="n">
         <v>1.2</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -712,6 +782,14 @@
       <c r="I9" t="n">
         <v>0.8</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -738,6 +816,14 @@
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -764,6 +850,14 @@
       <c r="I11" t="n">
         <v>2</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -790,6 +884,14 @@
       <c r="I12" t="n">
         <v>0.9</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -815,6 +917,289 @@
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>201005</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>201004</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>201005</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>201004</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>201005</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>201001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>201003</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>201002</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
